--- a/docs/海大快递站平面图-2026-09-29-用户精确版.xlsx
+++ b/docs/海大快递站平面图-2026-09-29-用户精确版.xlsx
@@ -2037,7 +2037,7 @@
       <c r="AT16" s="21" t="n"/>
       <c r="AU16" s="4" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="AV16" s="20" t="n"/>
@@ -2047,7 +2047,7 @@
       <c r="AZ16" s="21" t="n"/>
       <c r="BA16" s="4" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="BB16" s="20" t="n"/>
@@ -2057,7 +2057,7 @@
       <c r="BF16" s="21" t="n"/>
       <c r="BG16" s="4" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="BH16" s="20" t="n"/>
@@ -2067,7 +2067,7 @@
       <c r="BL16" s="21" t="n"/>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="BN16" s="20" t="n"/>
@@ -2077,7 +2077,7 @@
       <c r="BR16" s="21" t="n"/>
       <c r="BS16" s="4" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="BT16" s="20" t="n"/>
@@ -2087,7 +2087,7 @@
       <c r="BX16" s="21" t="n"/>
       <c r="BY16" s="4" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="BZ16" s="20" t="n"/>
@@ -2097,7 +2097,7 @@
       <c r="CD16" s="21" t="n"/>
       <c r="CE16" s="4" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="CF16" s="20" t="n"/>
@@ -2201,7 +2201,7 @@
       <c r="AT17" s="21" t="n"/>
       <c r="AU17" s="4" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="AV17" s="20" t="n"/>
@@ -2211,7 +2211,7 @@
       <c r="AZ17" s="21" t="n"/>
       <c r="BA17" s="4" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="BB17" s="20" t="n"/>
@@ -2221,7 +2221,7 @@
       <c r="BF17" s="21" t="n"/>
       <c r="BG17" s="4" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="BH17" s="20" t="n"/>
@@ -2231,7 +2231,7 @@
       <c r="BL17" s="21" t="n"/>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="BN17" s="20" t="n"/>
@@ -2241,7 +2241,7 @@
       <c r="BR17" s="21" t="n"/>
       <c r="BS17" s="4" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="BT17" s="20" t="n"/>
@@ -2251,7 +2251,7 @@
       <c r="BX17" s="21" t="n"/>
       <c r="BY17" s="4" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="BZ17" s="20" t="n"/>
@@ -2261,7 +2261,7 @@
       <c r="CD17" s="21" t="n"/>
       <c r="CE17" s="4" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="CF17" s="20" t="n"/>

--- a/docs/海大快递站平面图-2026-09-29-用户精确版.xlsx
+++ b/docs/海大快递站平面图-2026-09-29-用户精确版.xlsx
@@ -2037,7 +2037,7 @@
       <c r="AT16" s="21" t="n"/>
       <c r="AU16" s="4" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="AV16" s="20" t="n"/>
@@ -2047,7 +2047,7 @@
       <c r="AZ16" s="21" t="n"/>
       <c r="BA16" s="4" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="BB16" s="20" t="n"/>
@@ -2057,7 +2057,7 @@
       <c r="BF16" s="21" t="n"/>
       <c r="BG16" s="4" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="BH16" s="20" t="n"/>
@@ -2067,7 +2067,7 @@
       <c r="BL16" s="21" t="n"/>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="BN16" s="20" t="n"/>
@@ -2077,7 +2077,7 @@
       <c r="BR16" s="21" t="n"/>
       <c r="BS16" s="4" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="BT16" s="20" t="n"/>
@@ -2087,7 +2087,7 @@
       <c r="BX16" s="21" t="n"/>
       <c r="BY16" s="4" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="BZ16" s="20" t="n"/>
@@ -2097,7 +2097,7 @@
       <c r="CD16" s="21" t="n"/>
       <c r="CE16" s="4" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="CF16" s="20" t="n"/>
@@ -2201,7 +2201,7 @@
       <c r="AT17" s="21" t="n"/>
       <c r="AU17" s="4" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="AV17" s="20" t="n"/>
@@ -2211,7 +2211,7 @@
       <c r="AZ17" s="21" t="n"/>
       <c r="BA17" s="4" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="BB17" s="20" t="n"/>
@@ -2221,7 +2221,7 @@
       <c r="BF17" s="21" t="n"/>
       <c r="BG17" s="4" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="BH17" s="20" t="n"/>
@@ -2231,7 +2231,7 @@
       <c r="BL17" s="21" t="n"/>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="BN17" s="20" t="n"/>
@@ -2241,7 +2241,7 @@
       <c r="BR17" s="21" t="n"/>
       <c r="BS17" s="4" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="BT17" s="20" t="n"/>
@@ -2251,7 +2251,7 @@
       <c r="BX17" s="21" t="n"/>
       <c r="BY17" s="4" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="BZ17" s="20" t="n"/>
@@ -2261,7 +2261,7 @@
       <c r="CD17" s="21" t="n"/>
       <c r="CE17" s="4" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="CF17" s="20" t="n"/>
